--- a/artfynd/A 30004-2024 artfynd.xlsx
+++ b/artfynd/A 30004-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119507223</v>
+        <v>119506041</v>
       </c>
       <c r="B2" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550035</v>
+        <v>549960</v>
       </c>
       <c r="R2" t="n">
-        <v>6681184</v>
+        <v>6681284</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506567</v>
+        <v>119505781</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550141</v>
+        <v>549900</v>
       </c>
       <c r="R3" t="n">
-        <v>6681146</v>
+        <v>6681277</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119505523</v>
+        <v>119507274</v>
       </c>
       <c r="B4" t="n">
         <v>90562</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549854</v>
+        <v>549942</v>
       </c>
       <c r="R4" t="n">
-        <v>6681352</v>
+        <v>6681209</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506495</v>
+        <v>119506567</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>91254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550209</v>
+        <v>550141</v>
       </c>
       <c r="R5" t="n">
-        <v>6681183</v>
+        <v>6681146</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119506026</v>
+        <v>119506713</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549950</v>
+        <v>550041</v>
       </c>
       <c r="R7" t="n">
-        <v>6681281</v>
+        <v>6681134</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506041</v>
+        <v>119505523</v>
       </c>
       <c r="B8" t="n">
         <v>90562</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549960</v>
+        <v>549854</v>
       </c>
       <c r="R8" t="n">
-        <v>6681284</v>
+        <v>6681352</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119507274</v>
+        <v>119506495</v>
       </c>
       <c r="B9" t="n">
         <v>90562</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549942</v>
+        <v>550209</v>
       </c>
       <c r="R9" t="n">
-        <v>6681209</v>
+        <v>6681183</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119507252</v>
+        <v>119507223</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549981</v>
+        <v>550035</v>
       </c>
       <c r="R10" t="n">
-        <v>6681216</v>
+        <v>6681184</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506713</v>
+        <v>119506026</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550041</v>
+        <v>549950</v>
       </c>
       <c r="R11" t="n">
-        <v>6681134</v>
+        <v>6681281</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119505781</v>
+        <v>119507252</v>
       </c>
       <c r="B12" t="n">
         <v>90562</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549900</v>
+        <v>549981</v>
       </c>
       <c r="R12" t="n">
-        <v>6681277</v>
+        <v>6681216</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
